--- a/engine/gbco_study/GBCO_Valuation_Model_07092026_public.xlsx
+++ b/engine/gbco_study/GBCO_Valuation_Model_07092026_public.xlsx
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>30.14 (+4.0%)</t>
+          <t>30.69 (+4.0%)</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>26.3 - 34.6  (-9% / +19%)</t>
+          <t>26.8 - 35.2  (-9% / +19%)</t>
         </is>
       </c>
     </row>
@@ -2751,19 +2751,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>23.6001</v>
+        <v>24.0317</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>27.1428</v>
+        <v>27.6392</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>29.3711</v>
+        <v>29.9082</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>31.7904</v>
+        <v>32.3718</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>36.6397</v>
+        <v>37.3098</v>
       </c>
     </row>
     <row r="15">
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20.6273</v>
+        <v>21.0045</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>26.3232</v>
+        <v>26.8046</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>30.1383</v>
+        <v>30.6895</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>34.5525</v>
+        <v>35.1844</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>44.0823</v>
+        <v>44.8885</v>
       </c>
     </row>
     <row r="17">
@@ -2857,10 +2857,10 @@
         <v>40</v>
       </c>
       <c r="B24" s="10" t="n">
-        <v>0.02878</v>
+        <v>0.0347</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>0.1617</v>
+        <v>0.1821</v>
       </c>
     </row>
     <row r="25">
@@ -2868,10 +2868,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="10" t="n">
-        <v>0.04962</v>
+        <v>0.06214</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.22722</v>
+        <v>0.25656</v>
       </c>
     </row>
     <row r="26">
@@ -2879,10 +2879,10 @@
         <v>36</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>0.09488000000000001</v>
+        <v>0.11672</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>0.3228</v>
+        <v>0.36168</v>
       </c>
     </row>
     <row r="27">
@@ -2890,10 +2890,10 @@
         <v>34</v>
       </c>
       <c r="B27" s="10" t="n">
-        <v>0.18812</v>
+        <v>0.23456</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>0.46032</v>
+        <v>0.50962</v>
       </c>
     </row>
     <row r="28">
@@ -2901,10 +2901,10 @@
         <v>32</v>
       </c>
       <c r="B28" s="10" t="n">
-        <v>0.37654</v>
+        <v>0.45508</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>0.6361</v>
+        <v>0.69446</v>
       </c>
     </row>
     <row r="29">
@@ -2912,10 +2912,10 @@
         <v>30</v>
       </c>
       <c r="B29" s="10" t="n">
-        <v>0.70448</v>
+        <v>0.8072</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>0.84532</v>
+        <v>0.9008</v>
       </c>
     </row>
     <row r="30">
@@ -2923,10 +2923,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="n">
-        <v>0.6341</v>
+        <v>0.52576</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>0.7614</v>
+        <v>0.6845</v>
       </c>
     </row>
     <row r="31">
@@ -2934,10 +2934,10 @@
         <v>26</v>
       </c>
       <c r="B31" s="10" t="n">
-        <v>0.2752</v>
+        <v>0.22022</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>0.4786</v>
+        <v>0.4228</v>
       </c>
     </row>
     <row r="33">

--- a/engine/gbco_study/GBCO_Valuation_Model_07092026_public.xlsx
+++ b/engine/gbco_study/GBCO_Valuation_Model_07092026_public.xlsx
@@ -899,23 +899,23 @@
         <v>13389.1</v>
       </c>
       <c r="E6" s="23">
-        <f>D6+Assumptions!$C$79+Assumptions!$C$80-'Income Statement'!E18</f>
+        <f>D6+Assumptions!$C$82+Assumptions!$C$83-'Income Statement'!E18</f>
         <v/>
       </c>
       <c r="F6" s="23">
-        <f>E6+Assumptions!$D$79+Assumptions!$D$80-'Income Statement'!F18</f>
+        <f>E6+Assumptions!$D$82+Assumptions!$D$83-'Income Statement'!F18</f>
         <v/>
       </c>
       <c r="G6" s="23">
-        <f>F6+Assumptions!$E$79+Assumptions!$E$80-'Income Statement'!G18</f>
+        <f>F6+Assumptions!$E$82+Assumptions!$E$83-'Income Statement'!G18</f>
         <v/>
       </c>
       <c r="H6" s="23">
-        <f>G6+Assumptions!$F$79+Assumptions!$F$80-'Income Statement'!H18</f>
+        <f>G6+Assumptions!$F$82+Assumptions!$F$83-'Income Statement'!H18</f>
         <v/>
       </c>
       <c r="I6" s="23">
-        <f>H6+Assumptions!$G$79+Assumptions!$G$80-'Income Statement'!I18</f>
+        <f>H6+Assumptions!$G$82+Assumptions!$G$83-'Income Statement'!I18</f>
         <v/>
       </c>
     </row>
@@ -935,23 +935,23 @@
         <v>13689.5</v>
       </c>
       <c r="E7" s="14">
-        <f>D7+Assumptions!$C$90</f>
+        <f>D7+Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>E7+Assumptions!$D$90</f>
+        <f>E7+Assumptions!$D$93</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>F7+Assumptions!$E$90</f>
+        <f>F7+Assumptions!$E$93</f>
         <v/>
       </c>
       <c r="H7" s="14">
-        <f>G7+Assumptions!$F$90</f>
+        <f>G7+Assumptions!$F$93</f>
         <v/>
       </c>
       <c r="I7" s="14">
-        <f>H7+Assumptions!$G$90</f>
+        <f>H7+Assumptions!$G$93</f>
         <v/>
       </c>
     </row>
@@ -971,23 +971,23 @@
         <v>17518.3</v>
       </c>
       <c r="E8" s="14">
-        <f>D8*(1+Assumptions!$C$73)</f>
+        <f>D8*(1+Assumptions!$C$76)</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>E8*(1+Assumptions!$D$73)</f>
+        <f>E8*(1+Assumptions!$D$76)</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>F8*(1+Assumptions!$E$73)</f>
+        <f>F8*(1+Assumptions!$E$76)</f>
         <v/>
       </c>
       <c r="H8" s="14">
-        <f>G8*(1+Assumptions!$F$73)</f>
+        <f>G8*(1+Assumptions!$F$76)</f>
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>H8*(1+Assumptions!$G$73)</f>
+        <f>H8*(1+Assumptions!$G$76)</f>
         <v/>
       </c>
     </row>
@@ -1007,23 +1007,23 @@
         <v>24649.7</v>
       </c>
       <c r="E9" s="23">
-        <f>Segments!E15*Assumptions!$C$82</f>
+        <f>Segments!E15*Assumptions!$C$85</f>
         <v/>
       </c>
       <c r="F9" s="23">
-        <f>Segments!F15*Assumptions!$D$82</f>
+        <f>Segments!F15*Assumptions!$D$85</f>
         <v/>
       </c>
       <c r="G9" s="23">
-        <f>Segments!G15*Assumptions!$E$82</f>
+        <f>Segments!G15*Assumptions!$E$85</f>
         <v/>
       </c>
       <c r="H9" s="23">
-        <f>Segments!H15*Assumptions!$F$82</f>
+        <f>Segments!H15*Assumptions!$F$85</f>
         <v/>
       </c>
       <c r="I9" s="23">
-        <f>Segments!I15*Assumptions!$G$82</f>
+        <f>Segments!I15*Assumptions!$G$85</f>
         <v/>
       </c>
     </row>
@@ -1043,23 +1043,23 @@
         <v>5316.9</v>
       </c>
       <c r="E10" s="23">
-        <f>Segments!E15*Assumptions!$C$83</f>
+        <f>Segments!E15*Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="F10" s="23">
-        <f>Segments!F15*Assumptions!$D$83</f>
+        <f>Segments!F15*Assumptions!$D$86</f>
         <v/>
       </c>
       <c r="G10" s="23">
-        <f>Segments!G15*Assumptions!$E$83</f>
+        <f>Segments!G15*Assumptions!$E$86</f>
         <v/>
       </c>
       <c r="H10" s="23">
-        <f>Segments!H15*Assumptions!$F$83</f>
+        <f>Segments!H15*Assumptions!$F$86</f>
         <v/>
       </c>
       <c r="I10" s="23">
-        <f>Segments!I15*Assumptions!$G$83</f>
+        <f>Segments!I15*Assumptions!$G$86</f>
         <v/>
       </c>
     </row>
@@ -1079,23 +1079,23 @@
         <v>4670.6</v>
       </c>
       <c r="E11" s="23">
-        <f>Segments!E15*Assumptions!$C$84</f>
+        <f>Segments!E15*Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="F11" s="23">
-        <f>Segments!F15*Assumptions!$D$84</f>
+        <f>Segments!F15*Assumptions!$D$87</f>
         <v/>
       </c>
       <c r="G11" s="23">
-        <f>Segments!G15*Assumptions!$E$84</f>
+        <f>Segments!G15*Assumptions!$E$87</f>
         <v/>
       </c>
       <c r="H11" s="23">
-        <f>Segments!H15*Assumptions!$F$84</f>
+        <f>Segments!H15*Assumptions!$F$87</f>
         <v/>
       </c>
       <c r="I11" s="23">
-        <f>Segments!I15*Assumptions!$G$84</f>
+        <f>Segments!I15*Assumptions!$G$87</f>
         <v/>
       </c>
     </row>
@@ -1337,23 +1337,23 @@
         <v>38041.4</v>
       </c>
       <c r="E19" s="14">
-        <f>D19+Assumptions!$C$93</f>
+        <f>D19+Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F19" s="14">
-        <f>E19+Assumptions!$D$93</f>
+        <f>E19+Assumptions!$D$96</f>
         <v/>
       </c>
       <c r="G19" s="14">
-        <f>F19+Assumptions!$E$93</f>
+        <f>F19+Assumptions!$E$96</f>
         <v/>
       </c>
       <c r="H19" s="14">
-        <f>G19+Assumptions!$F$93</f>
+        <f>G19+Assumptions!$F$96</f>
         <v/>
       </c>
       <c r="I19" s="14">
-        <f>H19+Assumptions!$G$93</f>
+        <f>H19+Assumptions!$G$96</f>
         <v/>
       </c>
     </row>
@@ -1373,23 +1373,23 @@
         <v>18436.5</v>
       </c>
       <c r="E20" s="14">
-        <f>Segments!E15*Assumptions!$C$85+$B$30</f>
+        <f>Segments!E15*Assumptions!$C$88+$B$30</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>Segments!F15*Assumptions!$D$85+$B$30</f>
+        <f>Segments!F15*Assumptions!$D$88+$B$30</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>Segments!G15*Assumptions!$E$85+$B$30</f>
+        <f>Segments!G15*Assumptions!$E$88+$B$30</f>
         <v/>
       </c>
       <c r="H20" s="14">
-        <f>Segments!H15*Assumptions!$F$85+$B$30</f>
+        <f>Segments!H15*Assumptions!$F$88+$B$30</f>
         <v/>
       </c>
       <c r="I20" s="14">
-        <f>Segments!I15*Assumptions!$G$85+$B$30</f>
+        <f>Segments!I15*Assumptions!$G$88+$B$30</f>
         <v/>
       </c>
     </row>
@@ -1988,23 +1988,23 @@
         </is>
       </c>
       <c r="E12" s="23">
-        <f>-Assumptions!$C$79-Assumptions!$C$80</f>
+        <f>-Assumptions!$C$82-Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="F12" s="23">
-        <f>-Assumptions!$D$79-Assumptions!$D$80</f>
+        <f>-Assumptions!$D$82-Assumptions!$D$83</f>
         <v/>
       </c>
       <c r="G12" s="23">
-        <f>-Assumptions!$E$79-Assumptions!$E$80</f>
+        <f>-Assumptions!$E$82-Assumptions!$E$83</f>
         <v/>
       </c>
       <c r="H12" s="23">
-        <f>-Assumptions!$F$79-Assumptions!$F$80</f>
+        <f>-Assumptions!$F$82-Assumptions!$F$83</f>
         <v/>
       </c>
       <c r="I12" s="23">
-        <f>-Assumptions!$G$79-Assumptions!$G$80</f>
+        <f>-Assumptions!$G$82-Assumptions!$G$83</f>
         <v/>
       </c>
     </row>
@@ -2042,23 +2042,23 @@
         </is>
       </c>
       <c r="E14" s="23">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F14" s="23">
-        <f>Assumptions!$D$93</f>
+        <f>Assumptions!$D$96</f>
         <v/>
       </c>
       <c r="G14" s="23">
-        <f>Assumptions!$E$93</f>
+        <f>Assumptions!$E$96</f>
         <v/>
       </c>
       <c r="H14" s="23">
-        <f>Assumptions!$F$93</f>
+        <f>Assumptions!$F$96</f>
         <v/>
       </c>
       <c r="I14" s="23">
-        <f>Assumptions!$G$93</f>
+        <f>Assumptions!$G$96</f>
         <v/>
       </c>
     </row>
@@ -2069,23 +2069,23 @@
         </is>
       </c>
       <c r="E15" s="23">
-        <f>-'Income Statement'!E26*Assumptions!$C$94</f>
+        <f>-'Income Statement'!E26*Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="F15" s="23">
-        <f>-'Income Statement'!F26*Assumptions!$D$94</f>
+        <f>-'Income Statement'!F26*Assumptions!$D$97</f>
         <v/>
       </c>
       <c r="G15" s="23">
-        <f>-'Income Statement'!G26*Assumptions!$E$94</f>
+        <f>-'Income Statement'!G26*Assumptions!$E$97</f>
         <v/>
       </c>
       <c r="H15" s="23">
-        <f>-'Income Statement'!H26*Assumptions!$F$94</f>
+        <f>-'Income Statement'!H26*Assumptions!$F$97</f>
         <v/>
       </c>
       <c r="I15" s="23">
-        <f>-'Income Statement'!I26*Assumptions!$G$94</f>
+        <f>-'Income Statement'!I26*Assumptions!$G$97</f>
         <v/>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="B18" s="33">
-        <f>Assumptions!$B$59</f>
+        <f>Assumptions!$B$62</f>
         <v/>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B19" s="33">
-        <f>Assumptions!$B$60</f>
+        <f>Assumptions!$B$63</f>
         <v/>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="B20" s="33">
-        <f>Assumptions!$B$61</f>
+        <f>Assumptions!$B$64</f>
         <v/>
       </c>
     </row>
@@ -3006,19 +3006,19 @@
         </is>
       </c>
       <c r="B5" s="34">
-        <f>Assumptions!$B$45*0.5</f>
+        <f>Assumptions!$B$48*0.5</f>
         <v/>
       </c>
       <c r="C5" s="34">
-        <f>Assumptions!$B$46</f>
+        <f>Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="D5" s="34">
-        <f>Assumptions!$B$45*0.75</f>
+        <f>Assumptions!$B$48*0.75</f>
         <v/>
       </c>
       <c r="E5" s="34">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$48</f>
         <v/>
       </c>
     </row>
@@ -3027,19 +3027,19 @@
         <v>-0.02</v>
       </c>
       <c r="B6" s="19">
-        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+B$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+B$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+C$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+C$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="19">
-        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+D$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+D$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="19">
-        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+E$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A6*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+E$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3048,19 +3048,19 @@
         <v>-0.01</v>
       </c>
       <c r="B7" s="19">
-        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+B$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+B$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+C$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+C$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="19">
-        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+D$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+D$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="19">
-        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+E$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A7*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+E$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3069,19 +3069,19 @@
         <v>0</v>
       </c>
       <c r="B8" s="19">
-        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+B$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+B$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+C$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+C$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+D$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+D$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+E$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A8*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+E$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3090,19 +3090,19 @@
         <v>0.01</v>
       </c>
       <c r="B9" s="19">
-        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+B$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+B$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+C$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+C$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+D$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+D$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="19">
-        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+E$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A9*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+E$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3111,19 +3111,19 @@
         <v>0.02</v>
       </c>
       <c r="B10" s="19">
-        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+B$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+B$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+C$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+C$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+D$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+D$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E10" s="19">
-        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+E$5+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$23+$A10*100*DCF!$B$30-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+E$5+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3148,23 +3148,23 @@
         </is>
       </c>
       <c r="B14" s="36">
-        <f>Assumptions!$B$17+-0.02</f>
+        <f>Assumptions!$B$19+-0.02</f>
         <v/>
       </c>
       <c r="C14" s="36">
-        <f>Assumptions!$B$17+-0.01</f>
+        <f>Assumptions!$B$19+-0.01</f>
         <v/>
       </c>
       <c r="D14" s="36">
-        <f>Assumptions!$B$17+0.0</f>
+        <f>Assumptions!$B$19+0.0</f>
         <v/>
       </c>
       <c r="E14" s="36">
-        <f>Assumptions!$B$17+0.01</f>
+        <f>Assumptions!$B$19+0.01</f>
         <v/>
       </c>
       <c r="F14" s="36">
-        <f>Assumptions!$B$17+0.02</f>
+        <f>Assumptions!$B$19+0.02</f>
         <v/>
       </c>
     </row>
@@ -3173,23 +3173,23 @@
         <v>-0.02</v>
       </c>
       <c r="B15" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+B$14)/($G$23-B$14)*$F$23-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+B$14)/($G$23-B$14)*$F$23-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C15" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+C$14)/($G$23-C$14)*$F$23-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+C$14)/($G$23-C$14)*$F$23-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D15" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+D$14)/($G$23-D$14)*$F$23-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+D$14)/($G$23-D$14)*$F$23-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E15" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+E$14)/($G$23-E$14)*$F$23-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+E$14)/($G$23-E$14)*$F$23-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F15" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+F$14)/($G$23-F$14)*$F$23-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$23:$F$23)+DCF!$F$14*(1+F$14)/($G$23-F$14)*$F$23-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3198,23 +3198,23 @@
         <v>-0.01</v>
       </c>
       <c r="B16" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+B$14)/($G$24-B$14)*$F$24-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+B$14)/($G$24-B$14)*$F$24-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C16" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+C$14)/($G$24-C$14)*$F$24-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+C$14)/($G$24-C$14)*$F$24-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D16" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+D$14)/($G$24-D$14)*$F$24-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+D$14)/($G$24-D$14)*$F$24-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E16" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+E$14)/($G$24-E$14)*$F$24-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+E$14)/($G$24-E$14)*$F$24-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F16" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+F$14)/($G$24-F$14)*$F$24-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$24:$F$24)+DCF!$F$14*(1+F$14)/($G$24-F$14)*$F$24-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3223,23 +3223,23 @@
         <v>0</v>
       </c>
       <c r="B17" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+B$14)/($G$25-B$14)*$F$25-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+B$14)/($G$25-B$14)*$F$25-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C17" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+C$14)/($G$25-C$14)*$F$25-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+C$14)/($G$25-C$14)*$F$25-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D17" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+D$14)/($G$25-D$14)*$F$25-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+D$14)/($G$25-D$14)*$F$25-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E17" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+E$14)/($G$25-E$14)*$F$25-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+E$14)/($G$25-E$14)*$F$25-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F17" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+F$14)/($G$25-F$14)*$F$25-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$25:$F$25)+DCF!$F$14*(1+F$14)/($G$25-F$14)*$F$25-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3248,23 +3248,23 @@
         <v>0.01</v>
       </c>
       <c r="B18" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+B$14)/($G$26-B$14)*$F$26-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+B$14)/($G$26-B$14)*$F$26-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C18" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+C$14)/($G$26-C$14)*$F$26-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+C$14)/($G$26-C$14)*$F$26-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D18" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+D$14)/($G$26-D$14)*$F$26-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+D$14)/($G$26-D$14)*$F$26-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E18" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+E$14)/($G$26-E$14)*$F$26-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+E$14)/($G$26-E$14)*$F$26-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F18" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+F$14)/($G$26-F$14)*$F$26-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$26:$F$26)+DCF!$F$14*(1+F$14)/($G$26-F$14)*$F$26-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3273,23 +3273,23 @@
         <v>0.02</v>
       </c>
       <c r="B19" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+B$14)/($G$27-B$14)*$F$27-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+B$14)/($G$27-B$14)*$F$27-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C19" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+C$14)/($G$27-C$14)*$F$27-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+C$14)/($G$27-C$14)*$F$27-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D19" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+D$14)/($G$27-D$14)*$F$27-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+D$14)/($G$27-D$14)*$F$27-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E19" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+E$14)/($G$27-E$14)*$F$27-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+E$14)/($G$27-E$14)*$F$27-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F19" s="19">
-        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+F$14)/($G$27-F$14)*$F$27-Assumptions!$B$19-Assumptions!$B$20+Assumptions!$B$38+Assumptions!$B$48)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$14:$F$14,$B$27:$F$27)+DCF!$F$14*(1+F$14)/($G$27-F$14)*$F$27-Assumptions!$B$21-Assumptions!$B$22+Assumptions!$B$41+Assumptions!$B$51)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -3631,23 +3631,23 @@
         </is>
       </c>
       <c r="E7" s="19">
-        <f>'Income Statement'!E26*Assumptions!C$94/Assumptions!$B$6</f>
+        <f>'Income Statement'!E26*Assumptions!C$97/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="19">
-        <f>'Income Statement'!F26*Assumptions!D$94/Assumptions!$B$6</f>
+        <f>'Income Statement'!F26*Assumptions!D$97/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="G7" s="19">
-        <f>'Income Statement'!G26*Assumptions!E$94/Assumptions!$B$6</f>
+        <f>'Income Statement'!G26*Assumptions!E$97/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="H7" s="19">
-        <f>'Income Statement'!H26*Assumptions!F$94/Assumptions!$B$6</f>
+        <f>'Income Statement'!H26*Assumptions!F$97/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>'Income Statement'!I26*Assumptions!G$94/Assumptions!$B$6</f>
+        <f>'Income Statement'!I26*Assumptions!G$97/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -4424,14 +4424,14 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>28.5273</v>
+        <v>30.3773</v>
       </c>
       <c r="C7" s="25">
         <f>Summary!C7</f>
         <v/>
       </c>
       <c r="D7" s="7" t="n">
-        <v>85.4849</v>
+        <v>96.1336</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="C12" s="27">
-        <f>Assumptions!$B$40</f>
+        <f>Assumptions!$B$43</f>
         <v/>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -4529,7 +4529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4662,1464 +4662,1524 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity Ke = rf* + beta x ERP</t>
-        </is>
-      </c>
-      <c r="B12" s="13">
-        <f>B9+B10*B11</f>
-        <v/>
+          <t xml:space="preserve">   of which the mature equity premium — beta applies to THIS leg</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>0.04226800000000001</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>reproduces the committed schedule to the basis point.</t>
+          <t>the total premium less the country premium below. Beta measures how much more than the market this company moves; it is not a measure of how risky the country is, and multiplying the two charges the sovereign twice over for a cyclical name.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
+          <t xml:space="preserve">   of which the country premium — charged FLAT, once</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>0.2653</v>
+        <v>0.051832</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>the company's own effective borrowing rate, computed on the borrowings that actually bear the interest; the book is entirely local-currency on the disclosed facility note.</t>
+          <t>Egypt at 5.18% weighted by the 100% of operations that are here.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>After-tax cost of debt</t>
+          <t>Cost of equity Ke = rf* + beta x mature premium + country premium</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <f>B13*(1-B7)</f>
-        <v/>
+        <f>B9+B10*B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>reproduces the committed schedule to the basis point.</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Debt weight D/(D+E) — market-value equity</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>0.5745140347870709</v>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.2653</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>market capitalisation against disclosed borrowings; never book equity.</t>
+          <t>the company's own effective borrowing rate, computed on the borrowings that actually bear the interest; the book is entirely local-currency on the disclosed facility note.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>WACC — first forecast year</t>
+          <t>After-tax cost of debt</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <f>(1-B15)*B12+B15*B14</f>
-        <v/>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>the schedule GLIDES to a norm-built terminal of 14.18%; the DCF sheet carries one forward rate per year rather than this rate held for ever.</t>
-        </is>
+        <f>B15*(1-B7)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth (nominal EGP, DERIVED)</t>
+          <t>Debt weight D/(D+E) — market-value equity</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5745140347870709</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>stored as a REAL rate of 0.0% on the house Egyptian inflation path and recomputed to this nominal figure; a typed nominal rate is unfalsifiable.</t>
+          <t>market capitalisation against disclosed borrowings; never book equity.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>LEG 1 — GB AUTO: the cash-flow model's own bridge (the DCF sheet builds the leg)</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>WACC — first forecast year</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>(1-B17)*B14+B17*B16</f>
+        <v/>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>the schedule GLIDES to a norm-built terminal of 13.45%; the DCF sheet carries one forward rate per year rather than this rate held for ever.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>Terminal growth (nominal EGP, DERIVED)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>stored as a REAL rate of 0.0% on the house Egyptian inflation path and recomputed to this nominal figure; a typed nominal rate is unfalsifiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>LEG 1 — GB AUTO: the cash-flow model's own bridge (the DCF sheet builds the leg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>GB Auto net debt (30 June 2026, reviewed)</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B21" s="9" t="n">
         <v>14623.7</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>the bridge stands on the LATEST disclosed balance sheet and on the AUTO segment's own net debt, not the prior year end and not the group total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>GB Auto non-controlling interests (30 June 2026)</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>590.7</v>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>that leg's own minority, deducted from EQUITY value and never from enterprise value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>LEG 2 — GB CAPITAL: residual income, not book times one</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>GB Capital shareholders' equity before NCI, 30 June 2026</t>
+          <t>GB Auto non-controlling interests (30 June 2026)</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>22497.8</v>
+        <v>590.7</v>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>2Q26 earnings release, segmented balance sheet, GB Capital column.</t>
+          <t>that leg's own minority, deducted from EQUITY value and never from enterprise value.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>less: associates carried inside that segment, 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>16230.465</v>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>the reviewed consolidated interim balance sheet's own associates line. Taking it out is what stops the stake funding this leg AND being added back at its own mark.</t>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>LEG 2 — GB CAPITAL: residual income, not book times one</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>GB Capital operating equity</t>
-        </is>
-      </c>
-      <c r="B24" s="14">
-        <f>B22-B23</f>
-        <v/>
+          <t>GB Capital shareholders' equity before NCI, 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>22497.8</v>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>an identity off two disclosed figures, so nothing here is chosen.</t>
+          <t>2Q26 earnings release, segmented balance sheet, GB Capital column.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1H2026 GB Capital net profit after NCI</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>649.6</v>
+          <t>less: associates carried inside that segment, 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>16230.465</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>2Q26 earnings release, segment income statement.</t>
+          <t>the reviewed consolidated interim balance sheet's own associates line. Taking it out is what stops the stake funding this leg AND being added back at its own mark.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>1H2026 GB Capital investment gains from associates</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>426.2</v>
+          <t>GB Capital operating equity</t>
+        </is>
+      </c>
+      <c r="B26" s="14">
+        <f>B24-B25</f>
+        <v/>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>same table; taken out of the numerator because it is taken out of the base.</t>
+          <t>an identity off two disclosed figures, so nothing here is chosen.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>GB Capital equity before NCI, 31 December 2025</t>
+          <t>1H2026 GB Capital net profit after NCI</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
-        <v>18312.6</v>
+        <v>649.6</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>4Q25 earnings release, segmented balance sheet, GB Capital column.</t>
+          <t>2Q26 earnings release, segment income statement.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>less: associates carried inside it, 31 December 2025</t>
+          <t>1H2026 GB Capital investment gains from associates</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>15732.426</v>
+        <v>426.2</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>the reviewed balance sheet's own comparative column, which note 34 foots to.</t>
+          <t>same table; taken out of the numerator because it is taken out of the base.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>GB Capital operating equity, 31 December 2025</t>
-        </is>
-      </c>
-      <c r="B29" s="14">
-        <f>B27-B28</f>
-        <v/>
+          <t>GB Capital equity before NCI, 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>18312.6</v>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>4Q25 earnings release, segmented balance sheet, GB Capital column.</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Return on operating equity — 1H2026 annualised (ADOPTED)</t>
-        </is>
-      </c>
-      <c r="B30" s="13">
-        <f>(B25-B26)*2/((B29+B24)/2)</f>
-        <v/>
+          <t>less: associates carried inside it, 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>15732.426</v>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>a near-term reviewed actual outranks a stale full-year rate.</t>
+          <t>the reviewed balance sheet's own comparative column, which note 34 foots to.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>FY2025 GB Capital net profit after NCI</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>1365.9</v>
+          <t>GB Capital operating equity, 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B31" s="14">
+        <f>B29-B30</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>FY2025 GB Capital investment gains from associates</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
-        <v>986.4</v>
+          <t>Return on operating equity — 1H2026 annualised (ADOPTED)</t>
+        </is>
+      </c>
+      <c r="B32" s="13">
+        <f>(B27-B28)*2/((B31+B26)/2)</f>
+        <v/>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>a near-term reviewed actual outranks a stale full-year rate.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Return on operating equity — FY2025 framing</t>
-        </is>
-      </c>
-      <c r="B33" s="13">
-        <f>(B31-B32)/B29</f>
-        <v/>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>the OTHER framing of a contested judgement worth more than 5% of the answer, published beside the adopted one rather than averaged with it.</t>
-        </is>
+          <t>FY2025 GB Capital net profit after NCI</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>1365.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>from the house macro path: terminal inflation plus the real-rate convention, derived and never quoted.</t>
-        </is>
+          <t>FY2025 GB Capital investment gains from associates</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>986.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>0.07000000000000001</v>
+          <t>Return on operating equity — FY2025 framing</t>
+        </is>
+      </c>
+      <c r="B35" s="13">
+        <f>(B33-B34)/B31</f>
+        <v/>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>the OTHER framing of a contested judgement worth more than 5% of the answer, published beside the adopted one rather than averaged with it.</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of equity Ke(T) = rf(T) + beta x ERP(T)</t>
-        </is>
-      </c>
-      <c r="B36" s="13">
-        <f>B34+B10*B35</f>
-        <v/>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>0.105</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>the same beta as the explicit window; the construction is named, not assumed.</t>
+          <t>from the house macro path: terminal inflation plus the real-rate convention, derived and never quoted.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Justified price-to-book = (ROE - g) / (Ke(T) - g)</t>
-        </is>
-      </c>
-      <c r="B37" s="16">
-        <f>(B30-B17)/(B36-B17)</f>
-        <v/>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>the residual-income identity in its terminal form. THE TERMINAL Ke IS THE GENEROUS END and it is used deliberately: the explicit-window Ke would put this leg at a fraction of the figure below.</t>
-        </is>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>GB Capital lending leg (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B38" s="18">
-        <f>B24*B37</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   of which the terminal country premium — charged FLAT, once</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>0.027732</v>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>the terminal premium splits the same way the explicit one does; a country premium that stops being multiplied by beta in year five and starts again in perpetuity would be two views of one sovereign.</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>memo: the same leg on the FY2025 return framing</t>
-        </is>
-      </c>
-      <c r="B39" s="14">
-        <f>B24*((B33-B17)/(B36-B17))</f>
+          <t>Terminal cost of equity Ke(T) = rf(T) + beta x mature premium + country premium</t>
+        </is>
+      </c>
+      <c r="B39" s="13">
+        <f>B36+B10*(B37-B38)+B38</f>
         <v/>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>published so a reader sees the choice and not only its result.</t>
+          <t>the same beta as the explicit window, on the mature leg only; the construction is named, not assumed.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>memo: GB Capital operating equity per share — a DISCLOSED FLOOR, never weighted</t>
-        </is>
-      </c>
-      <c r="B40" s="19">
-        <f>B24/B6</f>
-        <v/>
+          <t>Justified price-to-book = (ROE - g) / (Ke(T) - g)</t>
+        </is>
+      </c>
+      <c r="B40" s="16">
+        <f>(B32-B19)/(B39-B19)</f>
+        <v/>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>the residual-income identity in its terminal form. THE TERMINAL Ke IS THE GENEROUS END and it is used deliberately: the explicit-window Ke would put this leg at a fraction of the figure below.</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>LEG 3 — THE ASSOCIATES: the contested judgement, computed BOTH ways</t>
-        </is>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>GB Capital lending leg (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B41" s="18">
+        <f>B26*B40</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>MNT-Halan round valuation (USD mn, June-2026 first close)</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>1400</v>
+          <t>memo: the same leg on the FY2025 return framing</t>
+        </is>
+      </c>
+      <c r="B42" s="14">
+        <f>B26*((B35-B19)/(B39-B19))</f>
+        <v/>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>published so a reader sees the choice and not only its result.</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>GB Corp stake in MNT-Halan — the figure the company states</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>0.4161</v>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>GB Corp's own press release of 9 June 2026 on MNT-Halan's Al Ahly Capital-led capital increase: the stake 'will be adjusted to 41.61%, compared to 42.58% prior to the transaction'</t>
-        </is>
+          <t>memo: GB Capital operating equity per share — a DISCLOSED FLOOR, never weighted</t>
+        </is>
+      </c>
+      <c r="B43" s="19">
+        <f>B26/B6</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>EGP per USD applied to the mark</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>a flagged estimate, and material to this one line.</t>
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>LEG 3 — THE ASSOCIATES: the contested judgement, computed BOTH ways</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>BRANCH A — MNT-Halan at the June-2026 round price</t>
-        </is>
-      </c>
-      <c r="B45" s="18">
-        <f>B42*B43*B44</f>
-        <v/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>MNT-Halan round valuation (USD mn, June-2026 first close)</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>1400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>BRANCH B — MNT-Halan at its reviewed carrying value, 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="n">
-        <v>15733.523</v>
+          <t>GB Corp stake in MNT-Halan — the figure the company states</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>0.4161</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>note 34 to the reviewed consolidated interim statements. The review conclusion on those statements is QUALIFIED at exactly this line, so this branch is not a safe harbour either.</t>
+          <t>GB Corp's own press release of 9 June 2026 on MNT-Halan's Al Ahly Capital-led capital increase: the stake 'will be adjusted to 41.61%, compared to 42.58% prior to the transaction'</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Other associates (Bedaya, Kaf) — by identity off the note's own total</t>
-        </is>
-      </c>
-      <c r="B47" s="14">
-        <f>B23-B46</f>
-        <v/>
+          <t>EGP per USD applied to the mark</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>47.5</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>the total and the MNT-Halan row each foot; three smaller rows carry a reading ambiguity in one cell, so the residual is the figure that can be reproduced.</t>
+          <t>a flagged estimate, and material to this one line.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Associates — branch A (round price)</t>
-        </is>
-      </c>
-      <c r="B48" s="14">
-        <f>B45+B47</f>
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>BRANCH A — MNT-Halan at the June-2026 round price</t>
+        </is>
+      </c>
+      <c r="B48" s="18">
+        <f>B45*B46*B47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Associates — branch B (reviewed carrying value)</t>
-        </is>
-      </c>
-      <c r="B49" s="14">
-        <f>B46+B47</f>
-        <v/>
+          <t>BRANCH B — MNT-Halan at its reviewed carrying value, 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>15733.523</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>note 34 to the reviewed consolidated interim statements. The review conclusion on those statements is QUALIFIED at exactly this line, so this branch is not a safe harbour either.</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>CROSS-CHECK INPUTS — the relative multiple and the disclosed floor</t>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Other associates (Bedaya, Kaf) — by identity off the note's own total</t>
+        </is>
+      </c>
+      <c r="B50" s="14">
+        <f>B25-B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>the total and the MNT-Halan row each foot; three smaller rows carry a reading ambiguity in one cell, so the residual is the figure that can be reproduced.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>GB Corp close, year-end 2023 (EGP)</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>7.9</v>
+          <t>Associates — branch A (round price)</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B48+B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Net profit attributable, FY2023</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="n">
-        <v>1890.8</v>
+          <t>Associates — branch B (reviewed carrying value)</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49+B50</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>GB Corp close, year-end 2024 (EGP)</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="n">
-        <v>17.13</v>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK INPUTS — the relative multiple and the disclosed floor</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Net profit attributable, FY2024</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="n">
-        <v>2928.1</v>
+          <t>GB Corp close, year-end 2023 (EGP)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>7.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>GB Corp close, year-end 2025 (EGP)</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n">
-        <v>27</v>
+          <t>Net profit attributable, FY2023</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>1890.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Net profit attributable, FY2025</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n">
-        <v>2880</v>
+          <t>GB Corp close, year-end 2024 (EGP)</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>17.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Shareholders' equity before NCI, 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="n">
-        <v>33454.3</v>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>the disclosed floor. It is worth printing because the shares trade BELOW it.</t>
-        </is>
+          <t>Net profit attributable, FY2024</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n">
+        <v>2928.1</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>MONTE CARLO — a separate lens on a separate clock; engine outputs, not a sheet simulation</t>
-        </is>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>GB Corp close, year-end 2025 (EGP)</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Anchor volatility (HAR forecast, annualised)</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="n">
-        <v>0.4968</v>
+          <t>Net profit attributable, FY2025</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="n">
+        <v>2880</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Secular drift (daily log-return, expanding window)</t>
-        </is>
-      </c>
-      <c r="B60" s="20" t="n">
-        <v>0.000415</v>
+          <t>Shareholders' equity before NCI, 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>33454.3</v>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>the disclosed floor. It is worth printing because the shares trade BELOW it.</t>
+        </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Net factor drift per quarter</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>0.0146</v>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>MONTE CARLO — a separate lens on a separate clock; engine outputs, not a sheet simulation</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Paths / seed</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="inlineStr">
-        <is>
-          <t>50,000 / 42</t>
-        </is>
+          <t>Anchor volatility (HAR forecast, annualised)</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
+        <v>0.4968</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>FORECAST DRIVERS (FY26E–FY30E) — the units x ASP build; every driver disclosed</t>
-        </is>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Secular drift (daily log-return, expanding window)</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="n">
+        <v>0.000415</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Driver \ year</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Net factor drift per quarter</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n">
+        <v>0.0146</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>PC volume growth</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D65" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F65" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G65" s="10" t="n">
-        <v>0.06</v>
+          <t>Paths / seed</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="inlineStr">
+        <is>
+          <t>50,000 / 42</t>
+        </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>PC ASP growth</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D66" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F66" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G66" s="10" t="n">
-        <v>0.06</v>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>FORECAST DRIVERS (FY26E–FY30E) — the units x ASP build; every driver disclosed</t>
+        </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>CV&amp;CE volume growth</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D67" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F67" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G67" s="10" t="n">
-        <v>0.08</v>
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Driver \ year</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>CV&amp;CE ASP growth</t>
+          <t>PC volume growth</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Light-Mobility volume growth</t>
+          <t>PC ASP growth</t>
         </is>
       </c>
       <c r="C69" s="10" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Light-Mobility ASP growth</t>
+          <t>CV&amp;CE volume growth</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Trading revenue growth</t>
+          <t>CV&amp;CE ASP growth</t>
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="F71" s="10" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>GB Capital revenue growth</t>
+          <t>Light-Mobility volume growth</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>GB Capital loan-book growth</t>
+          <t>Light-Mobility ASP growth</t>
         </is>
       </c>
       <c r="C73" s="10" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.28</v>
+        <v>0.05</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Auto gross margin</t>
+          <t>Trading revenue growth</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>0.138</v>
+        <v>0.18</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.142</v>
+        <v>0.15</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.145</v>
+        <v>0.12</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>0.145</v>
+        <v>0.1</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>0.145</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Auto GS&amp;A (% of revenue)</t>
+          <t>GB Capital revenue growth</t>
         </is>
       </c>
       <c r="C75" s="10" t="n">
-        <v>0.073</v>
+        <v>0.45</v>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Auto other operating income (% rev)</t>
+          <t>GB Capital loan-book growth</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>0.012</v>
+        <v>0.35</v>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.012</v>
+        <v>0.28</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>0.012</v>
+        <v>0.24</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>0.012</v>
+        <v>0.2</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>0.012</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Auto provisions (% rev)</t>
+          <t>Auto gross margin</t>
         </is>
       </c>
       <c r="C77" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.138</v>
       </c>
       <c r="D77" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.142</v>
       </c>
       <c r="E77" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.145</v>
       </c>
       <c r="F77" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.145</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Auto D&amp;A (% of revenue)</t>
+          <t>Auto GS&amp;A (% of revenue)</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>0.011</v>
+        <v>0.073</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Auto capex (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E79" s="9" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F79" s="9" t="n">
-        <v>2600</v>
-      </c>
-      <c r="G79" s="9" t="n">
-        <v>2800</v>
+          <t>Auto other operating income (% rev)</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="D79" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>0.012</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Rental-fleet &amp; other capex (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="n">
-        <v>700</v>
-      </c>
-      <c r="D80" s="9" t="n">
-        <v>800</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>900</v>
-      </c>
-      <c r="F80" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G80" s="9" t="n">
-        <v>1100</v>
+          <t>Auto provisions (% rev)</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>-0.003</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>GB Capital D&amp;A (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="n">
-        <v>560</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>640</v>
-      </c>
-      <c r="E81" s="9" t="n">
-        <v>730</v>
-      </c>
-      <c r="F81" s="9" t="n">
-        <v>830</v>
-      </c>
-      <c r="G81" s="9" t="n">
-        <v>940</v>
+          <t>Auto D&amp;A (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Auto inventory (% of Auto rev)</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="D82" s="10" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F82" s="10" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="G82" s="10" t="n">
-        <v>0.296</v>
+          <t>Auto capex (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G82" s="9" t="n">
+        <v>2800</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Auto receivables (% of Auto rev)</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D83" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F83" s="10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G83" s="10" t="n">
-        <v>0.08</v>
+          <t>Rental-fleet &amp; other capex (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>1100</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Auto advances &amp; debtors (% rev)</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D84" s="10" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="F84" s="10" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="G84" s="10" t="n">
-        <v>0.0645</v>
+          <t>GB Capital D&amp;A (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>560</v>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>640</v>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>730</v>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="G84" s="9" t="n">
+        <v>940</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Auto payables (% of Auto rev)</t>
+          <t>Auto inventory (% of Auto rev)</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>0.245</v>
+        <v>0.36</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.237</v>
+        <v>0.338</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>0.2325</v>
+        <v>0.32</v>
       </c>
       <c r="F85" s="10" t="n">
-        <v>0.229</v>
+        <v>0.308</v>
       </c>
       <c r="G85" s="10" t="n">
-        <v>0.2255</v>
+        <v>0.296</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Group opex S&amp;M+Admin (% of group rev)</t>
+          <t>Auto receivables (% of Auto rev)</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
         <v>0.08</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>0.0775</v>
+        <v>0.08</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>Group other income (% of group rev)</t>
+          <t>Auto advances &amp; debtors (% rev)</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.011</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0675</v>
       </c>
       <c r="F87" s="10" t="n">
-        <v>0.011</v>
+        <v>0.066</v>
       </c>
       <c r="G87" s="10" t="n">
-        <v>0.011</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>Group provisions (% of group rev)</t>
+          <t>Auto payables (% of Auto rev)</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.245</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.237</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.2325</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.229</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.2255</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>GB Capital gross margin</t>
+          <t>Group opex S&amp;M+Admin (% of group rev)</t>
         </is>
       </c>
       <c r="C89" s="10" t="n">
-        <v>0.188</v>
+        <v>0.08</v>
       </c>
       <c r="D89" s="10" t="n">
-        <v>0.19</v>
+        <v>0.079</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>0.192</v>
+        <v>0.078</v>
       </c>
       <c r="F89" s="10" t="n">
-        <v>0.194</v>
+        <v>0.0775</v>
       </c>
       <c r="G89" s="10" t="n">
-        <v>0.196</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Associates income (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="n">
-        <v>1250</v>
-      </c>
-      <c r="D90" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="E90" s="9" t="n">
-        <v>1630</v>
-      </c>
-      <c r="F90" s="9" t="n">
-        <v>1830</v>
-      </c>
-      <c r="G90" s="9" t="n">
-        <v>2030</v>
+          <t>Group other income (% of group rev)</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Net finance cost (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="n">
-        <v>-4100</v>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>-3800</v>
-      </c>
-      <c r="E91" s="9" t="n">
-        <v>-3500</v>
-      </c>
-      <c r="F91" s="9" t="n">
-        <v>-3300</v>
-      </c>
-      <c r="G91" s="9" t="n">
-        <v>-3100</v>
+          <t>Group provisions (% of group rev)</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F91" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>-0.003</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Minority interest (% of NP before MI)</t>
+          <t>GB Capital gross margin</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.188</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.19</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.192</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.194</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Increase in borrowings, net (EGP mn)</t>
+          <t>Associates income (EGP mn)</t>
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>5500</v>
+        <v>1250</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>5200</v>
+        <v>1430</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>5600</v>
+        <v>1630</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>5800</v>
+        <v>1830</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>6100</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Dividend payout (of attributable NP)</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D94" s="10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="F94" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G94" s="10" t="n">
-        <v>0.2</v>
+          <t>Net finance cost (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>-4100</v>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="9" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="F94" s="9" t="n">
+        <v>-3300</v>
+      </c>
+      <c r="G94" s="9" t="n">
+        <v>-3100</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Intercompany eliminations (% of gross revenue)</t>
+          <t>Minority interest (% of NP before MI)</t>
         </is>
       </c>
       <c r="C95" s="10" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="F95" s="10" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>0.011</v>
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Increase in borrowings, net (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>5600</v>
+      </c>
+      <c r="F96" s="9" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G96" s="9" t="n">
+        <v>6100</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>COST-OF-CAPITAL DETAIL (reference; the figures above are what the model reads)</t>
-        </is>
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Dividend payout (of attributable NP)</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D97" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F97" s="10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate — observed, and how it is normalised</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>The observed local-currency government bond yield of 23.00% less this sovereign's OWN default spread of 3.41%, giving 19.59%. Country risk then enters exactly once, inside the equity risk premium, rather than twice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Normalised risk-free rate rf* — rating basis</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="n">
-        <v>0.1663</v>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>the same observed yield of 23.00% less the RATING-basis default spread of 6.37%. The default spread stripped out and the premium added back must be on the same basis, or country risk is counted once and a half.</t>
-        </is>
+          <t>Intercompany eliminations (% of gross revenue)</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Equity risk premium — rating basis (the alternative to the adopted market basis)</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="n">
-        <v>0.1394</v>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>Both bases come from the same published country-risk file for this sovereign and both are published. The market basis is named CENTRAL because it is the market's own live pricing of that credit against an agency judgement updated in steps.</t>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>COST-OF-CAPITAL DETAIL (reference; the figures above are what the model reads)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity, alternative (rating-basis premium)</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>B99+B10*B100</f>
-        <v/>
+          <t>Risk-free rate — observed, and how it is normalised</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>The observed local-currency government bond yield of 23.00% less this sovereign's OWN default spread of 3.41%, giving 19.59%. Country risk then enters exactly once, inside the equity risk premium, rather than twice.</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Weighted cost of capital, alternative (rating-basis premium)</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>(1-B15)*B101+B15*B14</f>
-        <v/>
+          <t>Normalised risk-free rate rf* — rating basis</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>the same observed yield of 23.00% less the RATING-basis default spread of 6.37%. The default spread stripped out and the premium added back must be on the same basis, or country risk is counted once and a half.</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt — how it was produced</t>
-        </is>
+          <t>Equity risk premium — rating basis (the alternative to the adopted market basis)</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>0.1394</v>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>The company's own effective borrowing rate, computed independently from the filings on the borrowings that ACTUALLY BEAR THE INTEREST rather than on a broader liabilities total. Adopted 26.53% against a latest effective rate of 26.53% and a peak of 29.06%. The book is entirely local-currency on the disclosed facility note, so no foreign tranche is blended in.</t>
+          <t>Both bases come from the same published country-risk file for this sovereign and both are published. The market basis is named CENTRAL because it is the market's own live pricing of that credit against an agency judgement updated in steps.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>The schedule, not a single rate</t>
-        </is>
+          <t xml:space="preserve">   of which the country premium, rating basis — charged FLAT, once</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="n">
+        <v>0.09682400000000001</v>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>One forward rate per explicit year on the DCF sheet, gliding from 22.88% to a norm-built terminal of 14.18%, with the terminal brought home on the same cumulative factor as the last explicit year: one date, one price of time. The glide fractions are the policy-rate path's own cumulative progress rather than a second assumption.</t>
+          <t>the rating-basis premium of 13.94% less the same mature equity premium of 4.26% the market basis carries: the two bases differ in how the SOVEREIGN is read, not in what a mature equity market pays.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
+          <t>Cost of equity, alternative (rating-basis premium)</t>
+        </is>
+      </c>
+      <c r="B105" s="13">
+        <f>B102+B10*(B103-B104)+B104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Weighted cost of capital, alternative (rating-basis premium)</t>
+        </is>
+      </c>
+      <c r="B106" s="13">
+        <f>(1-B17)*B105+B17*B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt — how it was produced</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>The company's own effective borrowing rate, computed independently from the filings on the borrowings that ACTUALLY BEAR THE INTEREST rather than on a broader liabilities total. Adopted 26.53% against a latest effective rate of 26.53% and a peak of 29.06%. The book is entirely local-currency on the disclosed facility note, so no foreign tranche is blended in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>The schedule, not a single rate</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>One forward rate per explicit year on the DCF sheet, gliding from 23.12% to a norm-built terminal of 13.45%, with the terminal brought home on the same cumulative factor as the last explicit year: one date, one price of time. The glide fractions are the policy-rate path's own cumulative progress rather than a second assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
           <t>What is NOT on this sheet, and why</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>There is no complexity or conglomerate discount and there are no lens weights. Both were free parameters that had never cleared an out-of-sample test and nothing in the filings disclosed a basis for either. The uncertainty they stood in for is the associate mark, and it is carried as two branches from row 44 down to the last sheet.</t>
         </is>
@@ -6218,11 +6278,11 @@
         </is>
       </c>
       <c r="C7" s="23">
-        <f>Assumptions!$B$38</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>Assumptions!$B$38</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
     </row>
@@ -6238,11 +6298,11 @@
         </is>
       </c>
       <c r="C8" s="23">
-        <f>Assumptions!$B$49</f>
+        <f>Assumptions!$B$52</f>
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>Assumptions!$B$48</f>
+        <f>Assumptions!$B$51</f>
         <v/>
       </c>
     </row>
@@ -6333,11 +6393,11 @@
         </is>
       </c>
       <c r="C15" s="23">
-        <f>Assumptions!$B$46</f>
+        <f>Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$48</f>
         <v/>
       </c>
     </row>
@@ -6421,15 +6481,15 @@
     </row>
     <row r="24">
       <c r="A24" s="23">
-        <f>Assumptions!$B$45*0.5</f>
+        <f>Assumptions!$B$48*0.5</f>
         <v/>
       </c>
       <c r="B24" s="16">
-        <f>A24/Assumptions!$B$46</f>
+        <f>A24/Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="C24" s="19">
-        <f>(DCF!$B$27+Assumptions!$B$38+A24+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$27+Assumptions!$B$41+A24+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -6440,15 +6500,15 @@
     </row>
     <row r="25">
       <c r="A25" s="23">
-        <f>Assumptions!$B$46</f>
+        <f>Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="B25" s="16">
-        <f>A25/Assumptions!$B$46</f>
+        <f>A25/Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="C25" s="19">
-        <f>(DCF!$B$27+Assumptions!$B$38+A25+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$27+Assumptions!$B$41+A25+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -6459,15 +6519,15 @@
     </row>
     <row r="26">
       <c r="A26" s="23">
-        <f>Assumptions!$B$45*0.75</f>
+        <f>Assumptions!$B$48*0.75</f>
         <v/>
       </c>
       <c r="B26" s="16">
-        <f>A26/Assumptions!$B$46</f>
+        <f>A26/Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="C26" s="19">
-        <f>(DCF!$B$27+Assumptions!$B$38+A26+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$27+Assumptions!$B$41+A26+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -6478,15 +6538,15 @@
     </row>
     <row r="27">
       <c r="A27" s="23">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="B27" s="16">
-        <f>A27/Assumptions!$B$46</f>
+        <f>A27/Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="C27" s="19">
-        <f>(DCF!$B$27+Assumptions!$B$38+A27+Assumptions!$B$47)/Assumptions!$B$6</f>
+        <f>(DCF!$B$27+Assumptions!$B$41+A27+Assumptions!$B$50)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -6610,23 +6670,23 @@
         <v>56548</v>
       </c>
       <c r="E6" s="14">
-        <f>D6*(1+Assumptions!$C$65)</f>
+        <f>D6*(1+Assumptions!$C$68)</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>E6*(1+Assumptions!$D$65)</f>
+        <f>E6*(1+Assumptions!$D$68)</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>F6*(1+Assumptions!$E$65)</f>
+        <f>F6*(1+Assumptions!$E$68)</f>
         <v/>
       </c>
       <c r="H6" s="14">
-        <f>G6*(1+Assumptions!$F$65)</f>
+        <f>G6*(1+Assumptions!$F$68)</f>
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>H6*(1+Assumptions!$G$65)</f>
+        <f>H6*(1+Assumptions!$G$68)</f>
         <v/>
       </c>
     </row>
@@ -6685,23 +6745,23 @@
         <v/>
       </c>
       <c r="E8" s="19">
-        <f>D8*(1+Assumptions!$C$66)</f>
+        <f>D8*(1+Assumptions!$C$69)</f>
         <v/>
       </c>
       <c r="F8" s="19">
-        <f>E8*(1+Assumptions!$D$66)</f>
+        <f>E8*(1+Assumptions!$D$69)</f>
         <v/>
       </c>
       <c r="G8" s="19">
-        <f>F8*(1+Assumptions!$E$66)</f>
+        <f>F8*(1+Assumptions!$E$69)</f>
         <v/>
       </c>
       <c r="H8" s="19">
-        <f>G8*(1+Assumptions!$F$66)</f>
+        <f>G8*(1+Assumptions!$F$69)</f>
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>H8*(1+Assumptions!$G$66)</f>
+        <f>H8*(1+Assumptions!$G$69)</f>
         <v/>
       </c>
     </row>
@@ -6721,23 +6781,23 @@
         <v>3404</v>
       </c>
       <c r="E9" s="14">
-        <f>D9*(1+Assumptions!$C$67)</f>
+        <f>D9*(1+Assumptions!$C$70)</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>E9*(1+Assumptions!$D$67)</f>
+        <f>E9*(1+Assumptions!$D$70)</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>F9*(1+Assumptions!$E$67)</f>
+        <f>F9*(1+Assumptions!$E$70)</f>
         <v/>
       </c>
       <c r="H9" s="14">
-        <f>G9*(1+Assumptions!$F$67)</f>
+        <f>G9*(1+Assumptions!$F$70)</f>
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>H9*(1+Assumptions!$G$67)</f>
+        <f>H9*(1+Assumptions!$G$70)</f>
         <v/>
       </c>
     </row>
@@ -6757,23 +6817,23 @@
         <v>5956.8</v>
       </c>
       <c r="E10" s="14">
-        <f>D10*(1+Assumptions!$C$67)*(1+Assumptions!$C$68)</f>
+        <f>D10*(1+Assumptions!$C$70)*(1+Assumptions!$C$71)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>E10*(1+Assumptions!$D$67)*(1+Assumptions!$D$68)</f>
+        <f>E10*(1+Assumptions!$D$70)*(1+Assumptions!$D$71)</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>F10*(1+Assumptions!$E$67)*(1+Assumptions!$E$68)</f>
+        <f>F10*(1+Assumptions!$E$70)*(1+Assumptions!$E$71)</f>
         <v/>
       </c>
       <c r="H10" s="14">
-        <f>G10*(1+Assumptions!$F$67)*(1+Assumptions!$F$68)</f>
+        <f>G10*(1+Assumptions!$F$70)*(1+Assumptions!$F$71)</f>
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>H10*(1+Assumptions!$G$67)*(1+Assumptions!$G$68)</f>
+        <f>H10*(1+Assumptions!$G$70)*(1+Assumptions!$G$71)</f>
         <v/>
       </c>
     </row>
@@ -6793,23 +6853,23 @@
         <v>33906</v>
       </c>
       <c r="E11" s="14">
-        <f>D11*(1+Assumptions!$C$69)</f>
+        <f>D11*(1+Assumptions!$C$72)</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>E11*(1+Assumptions!$D$69)</f>
+        <f>E11*(1+Assumptions!$D$72)</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>F11*(1+Assumptions!$E$69)</f>
+        <f>F11*(1+Assumptions!$E$72)</f>
         <v/>
       </c>
       <c r="H11" s="14">
-        <f>G11*(1+Assumptions!$F$69)</f>
+        <f>G11*(1+Assumptions!$F$72)</f>
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>H11*(1+Assumptions!$G$69)</f>
+        <f>H11*(1+Assumptions!$G$72)</f>
         <v/>
       </c>
     </row>
@@ -6829,23 +6889,23 @@
         <v>2203.8</v>
       </c>
       <c r="E12" s="14">
-        <f>D12*(1+Assumptions!$C$69)*(1+Assumptions!$C$70)</f>
+        <f>D12*(1+Assumptions!$C$72)*(1+Assumptions!$C$73)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>E12*(1+Assumptions!$D$69)*(1+Assumptions!$D$70)</f>
+        <f>E12*(1+Assumptions!$D$72)*(1+Assumptions!$D$73)</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>F12*(1+Assumptions!$E$69)*(1+Assumptions!$E$70)</f>
+        <f>F12*(1+Assumptions!$E$72)*(1+Assumptions!$E$73)</f>
         <v/>
       </c>
       <c r="H12" s="14">
-        <f>G12*(1+Assumptions!$F$69)*(1+Assumptions!$F$70)</f>
+        <f>G12*(1+Assumptions!$F$72)*(1+Assumptions!$F$73)</f>
         <v/>
       </c>
       <c r="I12" s="14">
-        <f>H12*(1+Assumptions!$G$69)*(1+Assumptions!$G$70)</f>
+        <f>H12*(1+Assumptions!$G$72)*(1+Assumptions!$G$73)</f>
         <v/>
       </c>
     </row>
@@ -6865,23 +6925,23 @@
         <v>4242.8</v>
       </c>
       <c r="E13" s="14">
-        <f>D13*(1+Assumptions!$C$71)</f>
+        <f>D13*(1+Assumptions!$C$74)</f>
         <v/>
       </c>
       <c r="F13" s="14">
-        <f>E13*(1+Assumptions!$D$71)</f>
+        <f>E13*(1+Assumptions!$D$74)</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>F13*(1+Assumptions!$E$71)</f>
+        <f>F13*(1+Assumptions!$E$74)</f>
         <v/>
       </c>
       <c r="H13" s="14">
-        <f>G13*(1+Assumptions!$F$71)</f>
+        <f>G13*(1+Assumptions!$F$74)</f>
         <v/>
       </c>
       <c r="I13" s="14">
-        <f>H13*(1+Assumptions!$G$71)</f>
+        <f>H13*(1+Assumptions!$G$74)</f>
         <v/>
       </c>
     </row>
@@ -6976,23 +7036,23 @@
         <v>14743</v>
       </c>
       <c r="E16" s="14">
-        <f>D16*(1+Assumptions!$C$72)</f>
+        <f>D16*(1+Assumptions!$C$75)</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>E16*(1+Assumptions!$D$72)</f>
+        <f>E16*(1+Assumptions!$D$75)</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>F16*(1+Assumptions!$E$72)</f>
+        <f>F16*(1+Assumptions!$E$75)</f>
         <v/>
       </c>
       <c r="H16" s="14">
-        <f>G16*(1+Assumptions!$F$72)</f>
+        <f>G16*(1+Assumptions!$F$75)</f>
         <v/>
       </c>
       <c r="I16" s="14">
-        <f>H16*(1+Assumptions!$G$72)</f>
+        <f>H16*(1+Assumptions!$G$75)</f>
         <v/>
       </c>
     </row>
@@ -7015,23 +7075,23 @@
         <v/>
       </c>
       <c r="E17" s="14">
-        <f>-(E15+E16)*Assumptions!$C$95</f>
+        <f>-(E15+E16)*Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="F17" s="14">
-        <f>-(F15+F16)*Assumptions!$D$95</f>
+        <f>-(F15+F16)*Assumptions!$D$98</f>
         <v/>
       </c>
       <c r="G17" s="14">
-        <f>-(G15+G16)*Assumptions!$E$95</f>
+        <f>-(G15+G16)*Assumptions!$E$98</f>
         <v/>
       </c>
       <c r="H17" s="14">
-        <f>-(H15+H16)*Assumptions!$F$95</f>
+        <f>-(H15+H16)*Assumptions!$F$98</f>
         <v/>
       </c>
       <c r="I17" s="14">
-        <f>-(I15+I16)*Assumptions!$G$95</f>
+        <f>-(I15+I16)*Assumptions!$G$98</f>
         <v/>
       </c>
     </row>
@@ -7087,23 +7147,23 @@
         <v>9837.1</v>
       </c>
       <c r="E20" s="14">
-        <f>E15*Assumptions!$C$74</f>
+        <f>E15*Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>F15*Assumptions!$D$74</f>
+        <f>F15*Assumptions!$D$77</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>G15*Assumptions!$E$74</f>
+        <f>G15*Assumptions!$E$77</f>
         <v/>
       </c>
       <c r="H20" s="14">
-        <f>H15*Assumptions!$F$74</f>
+        <f>H15*Assumptions!$F$77</f>
         <v/>
       </c>
       <c r="I20" s="14">
-        <f>I15*Assumptions!$G$74</f>
+        <f>I15*Assumptions!$G$77</f>
         <v/>
       </c>
     </row>
@@ -7162,23 +7222,23 @@
         <v>5830.9</v>
       </c>
       <c r="E22" s="14">
-        <f>E20-E15*Assumptions!$C$75+E15*Assumptions!$C$76+E15*Assumptions!$C$77</f>
+        <f>E20-E15*Assumptions!$C$78+E15*Assumptions!$C$79+E15*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f>F20-F15*Assumptions!$D$75+F15*Assumptions!$D$76+F15*Assumptions!$D$77</f>
+        <f>F20-F15*Assumptions!$D$78+F15*Assumptions!$D$79+F15*Assumptions!$D$80</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>G20-G15*Assumptions!$E$75+G15*Assumptions!$E$76+G15*Assumptions!$E$77</f>
+        <f>G20-G15*Assumptions!$E$78+G15*Assumptions!$E$79+G15*Assumptions!$E$80</f>
         <v/>
       </c>
       <c r="H22" s="14">
-        <f>H20-H15*Assumptions!$F$75+H15*Assumptions!$F$76+H15*Assumptions!$F$77</f>
+        <f>H20-H15*Assumptions!$F$78+H15*Assumptions!$F$79+H15*Assumptions!$F$80</f>
         <v/>
       </c>
       <c r="I22" s="14">
-        <f>I20-I15*Assumptions!$G$75+I15*Assumptions!$G$76+I15*Assumptions!$G$77</f>
+        <f>I20-I15*Assumptions!$G$78+I15*Assumptions!$G$79+I15*Assumptions!$G$80</f>
         <v/>
       </c>
     </row>
@@ -7198,23 +7258,23 @@
         <v>683.3</v>
       </c>
       <c r="E23" s="14">
-        <f>E15*Assumptions!$C$78</f>
+        <f>E15*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f>F15*Assumptions!$D$78</f>
+        <f>F15*Assumptions!$D$81</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>G15*Assumptions!$E$78</f>
+        <f>G15*Assumptions!$E$81</f>
         <v/>
       </c>
       <c r="H23" s="14">
-        <f>H15*Assumptions!$F$78</f>
+        <f>H15*Assumptions!$F$81</f>
         <v/>
       </c>
       <c r="I23" s="14">
-        <f>I15*Assumptions!$G$78</f>
+        <f>I15*Assumptions!$G$81</f>
         <v/>
       </c>
     </row>
@@ -7441,11 +7501,11 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>Assumptions!$B$51</f>
+        <f>Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="C6" s="30">
-        <f>Assumptions!$B$52</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="D6" s="19">
@@ -7464,11 +7524,11 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>Assumptions!$B$53</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="C7" s="30">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$57</f>
         <v/>
       </c>
       <c r="D7" s="19">
@@ -7487,11 +7547,11 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$58</f>
         <v/>
       </c>
       <c r="C8" s="30">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$59</f>
         <v/>
       </c>
       <c r="D8" s="19">
@@ -7615,7 +7675,7 @@
         </is>
       </c>
       <c r="B20" s="23">
-        <f>Assumptions!$B$57</f>
+        <f>Assumptions!$B$60</f>
         <v/>
       </c>
     </row>
@@ -7901,23 +7961,23 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>-Assumptions!$C$79</f>
+        <f>-Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>-Assumptions!$D$79</f>
+        <f>-Assumptions!$D$82</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>-Assumptions!$E$79</f>
+        <f>-Assumptions!$E$82</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>-Assumptions!$F$79</f>
+        <f>-Assumptions!$F$82</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-Assumptions!$G$79</f>
+        <f>-Assumptions!$G$82</f>
         <v/>
       </c>
     </row>
@@ -7982,19 +8042,19 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>0.2287554134378177</v>
+        <v>0.2311662840904956</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.1976861075812545</v>
+        <v>0.1966574472650062</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.1728306628960039</v>
+        <v>0.1690503778046146</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.154189079382066</v>
+        <v>0.148345075709321</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.1417613570394407</v>
+        <v>0.1345415409791253</v>
       </c>
     </row>
     <row r="16">
@@ -8069,7 +8129,7 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>0.1417613570394407</v>
+        <v>0.1345415409791253</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -8084,7 +8144,7 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>F14*(1+Assumptions!$B$17)/(B20-Assumptions!$B$17)</f>
+        <f>F14*(1+Assumptions!$B$19)/(B20-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -8128,7 +8188,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>-Assumptions!$B$19</f>
+        <f>-Assumptions!$B$21</f>
         <v/>
       </c>
     </row>
@@ -8139,7 +8199,7 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>-Assumptions!$B$20</f>
+        <f>-Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
@@ -8150,7 +8210,7 @@
         </is>
       </c>
       <c r="B27" s="18">
-        <f>B23-Assumptions!$B$19-Assumptions!$B$20</f>
+        <f>B23-Assumptions!$B$21-Assumptions!$B$22</f>
         <v/>
       </c>
     </row>
@@ -8161,7 +8221,7 @@
         </is>
       </c>
       <c r="B29" s="13">
-        <f>B15-Assumptions!$B$16</f>
+        <f>B15-Assumptions!$B$18</f>
         <v/>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -8177,7 +8237,7 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>0.01*(1-Assumptions!$B$7)*(SUMPRODUCT(B6:F6,B16:F16)+F6*(1+Assumptions!$B$17)/(B20-Assumptions!$B$17)*F16)</f>
+        <f>0.01*(1-Assumptions!$B$7)*(SUMPRODUCT(B6:F6,B16:F16)+F6*(1+Assumptions!$B$19)/(B20-Assumptions!$B$19)*F16)</f>
         <v/>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -8457,23 +8517,23 @@
         <v>12431.1</v>
       </c>
       <c r="E10" s="23">
-        <f>Segments!E20+Segments!E16*Assumptions!$C$89+Segments!E17*0.2</f>
+        <f>Segments!E20+Segments!E16*Assumptions!$C$92+Segments!E17*0.2</f>
         <v/>
       </c>
       <c r="F10" s="23">
-        <f>Segments!F20+Segments!F16*Assumptions!$D$89+Segments!F17*0.2</f>
+        <f>Segments!F20+Segments!F16*Assumptions!$D$92+Segments!F17*0.2</f>
         <v/>
       </c>
       <c r="G10" s="23">
-        <f>Segments!G20+Segments!G16*Assumptions!$E$89+Segments!G17*0.2</f>
+        <f>Segments!G20+Segments!G16*Assumptions!$E$92+Segments!G17*0.2</f>
         <v/>
       </c>
       <c r="H10" s="23">
-        <f>Segments!H20+Segments!H16*Assumptions!$F$89+Segments!H17*0.2</f>
+        <f>Segments!H20+Segments!H16*Assumptions!$F$92+Segments!H17*0.2</f>
         <v/>
       </c>
       <c r="I10" s="23">
-        <f>Segments!I20+Segments!I16*Assumptions!$G$89+Segments!I17*0.2</f>
+        <f>Segments!I20+Segments!I16*Assumptions!$G$92+Segments!I17*0.2</f>
         <v/>
       </c>
     </row>
@@ -8532,23 +8592,23 @@
         <v>-6547.299999999999</v>
       </c>
       <c r="E12" s="14">
-        <f>-E9*Assumptions!$C$86</f>
+        <f>-E9*Assumptions!$C$89</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>-F9*Assumptions!$D$86</f>
+        <f>-F9*Assumptions!$D$89</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>-G9*Assumptions!$E$86</f>
+        <f>-G9*Assumptions!$E$89</f>
         <v/>
       </c>
       <c r="H12" s="14">
-        <f>-H9*Assumptions!$F$86</f>
+        <f>-H9*Assumptions!$F$89</f>
         <v/>
       </c>
       <c r="I12" s="14">
-        <f>-I9*Assumptions!$G$86</f>
+        <f>-I9*Assumptions!$G$89</f>
         <v/>
       </c>
     </row>
@@ -8568,23 +8628,23 @@
         <v>912.2</v>
       </c>
       <c r="E13" s="14">
-        <f>E9*Assumptions!$C$87</f>
+        <f>E9*Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="F13" s="14">
-        <f>F9*Assumptions!$D$87</f>
+        <f>F9*Assumptions!$D$90</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>G9*Assumptions!$E$87</f>
+        <f>G9*Assumptions!$E$90</f>
         <v/>
       </c>
       <c r="H13" s="14">
-        <f>H9*Assumptions!$F$87</f>
+        <f>H9*Assumptions!$F$90</f>
         <v/>
       </c>
       <c r="I13" s="14">
-        <f>I9*Assumptions!$G$87</f>
+        <f>I9*Assumptions!$G$90</f>
         <v/>
       </c>
     </row>
@@ -8604,23 +8664,23 @@
         <v>-165.1</v>
       </c>
       <c r="E14" s="14">
-        <f>E9*Assumptions!$C$88</f>
+        <f>E9*Assumptions!$C$91</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>F9*Assumptions!$D$88</f>
+        <f>F9*Assumptions!$D$91</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>G9*Assumptions!$E$88</f>
+        <f>G9*Assumptions!$E$91</f>
         <v/>
       </c>
       <c r="H14" s="14">
-        <f>H9*Assumptions!$F$88</f>
+        <f>H9*Assumptions!$F$91</f>
         <v/>
       </c>
       <c r="I14" s="14">
-        <f>I9*Assumptions!$G$88</f>
+        <f>I9*Assumptions!$G$91</f>
         <v/>
       </c>
     </row>
@@ -8679,23 +8739,23 @@
         <v>974.8</v>
       </c>
       <c r="E16" s="14">
-        <f>Assumptions!$C$90</f>
+        <f>Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>Assumptions!$D$90</f>
+        <f>Assumptions!$D$93</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>Assumptions!$E$90</f>
+        <f>Assumptions!$E$93</f>
         <v/>
       </c>
       <c r="H16" s="14">
-        <f>Assumptions!$F$90</f>
+        <f>Assumptions!$F$93</f>
         <v/>
       </c>
       <c r="I16" s="14">
-        <f>Assumptions!$G$90</f>
+        <f>Assumptions!$G$93</f>
         <v/>
       </c>
     </row>
@@ -8748,23 +8808,23 @@
         <v>999.3</v>
       </c>
       <c r="E18" s="23">
-        <f>Segments!E23+Assumptions!$C$81</f>
+        <f>Segments!E23+Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F18" s="23">
-        <f>Segments!F23+Assumptions!$D$81</f>
+        <f>Segments!F23+Assumptions!$D$84</f>
         <v/>
       </c>
       <c r="G18" s="23">
-        <f>Segments!G23+Assumptions!$E$81</f>
+        <f>Segments!G23+Assumptions!$E$84</f>
         <v/>
       </c>
       <c r="H18" s="23">
-        <f>Segments!H23+Assumptions!$F$81</f>
+        <f>Segments!H23+Assumptions!$F$84</f>
         <v/>
       </c>
       <c r="I18" s="23">
-        <f>Segments!I23+Assumptions!$G$81</f>
+        <f>Segments!I23+Assumptions!$G$84</f>
         <v/>
       </c>
     </row>
@@ -8851,23 +8911,23 @@
         <v>-3702.1</v>
       </c>
       <c r="E21" s="14">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f>Assumptions!$D$91</f>
+        <f>Assumptions!$D$94</f>
         <v/>
       </c>
       <c r="G21" s="14">
-        <f>Assumptions!$E$91</f>
+        <f>Assumptions!$E$94</f>
         <v/>
       </c>
       <c r="H21" s="14">
-        <f>Assumptions!$F$91</f>
+        <f>Assumptions!$F$94</f>
         <v/>
       </c>
       <c r="I21" s="14">
-        <f>Assumptions!$G$91</f>
+        <f>Assumptions!$G$94</f>
         <v/>
       </c>
     </row>
@@ -9001,23 +9061,23 @@
         <v>99.59999999999999</v>
       </c>
       <c r="E25" s="14">
-        <f>E24*Assumptions!$C$92</f>
+        <f>E24*Assumptions!$C$95</f>
         <v/>
       </c>
       <c r="F25" s="14">
-        <f>F24*Assumptions!$D$92</f>
+        <f>F24*Assumptions!$D$95</f>
         <v/>
       </c>
       <c r="G25" s="14">
-        <f>G24*Assumptions!$E$92</f>
+        <f>G24*Assumptions!$E$95</f>
         <v/>
       </c>
       <c r="H25" s="14">
-        <f>H24*Assumptions!$F$92</f>
+        <f>H24*Assumptions!$F$95</f>
         <v/>
       </c>
       <c r="I25" s="14">
-        <f>I24*Assumptions!$G$92</f>
+        <f>I24*Assumptions!$G$95</f>
         <v/>
       </c>
     </row>
